--- a/artfynd/A 13093-2025 artfynd.xlsx
+++ b/artfynd/A 13093-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>114400748</v>
       </c>
       <c r="B2" t="n">
-        <v>95923</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,6 +774,112 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>MSK0115 NVI Holm 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>114400452</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Stråkenäs, SO - Syd, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>362127</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6350048</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Varberg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Gunnarsjö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-11-15</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-11-15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ropandes</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Alexander Nordstrand</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Julia Svensson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
         <is>
           <t>MSK0115 NVI Holm 2023</t>
         </is>
